--- a/00-TrainRnns/tau-3/Y_otm/BestModels-otm.xlsx
+++ b/00-TrainRnns/tau-3/Y_otm/BestModels-otm.xlsx
@@ -477,182 +477,182 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2250</v>
+        <v>2668</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[76]</t>
+          <t>[89]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9943255528123531</v>
+        <v>0.9986545955373483</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9863250866823713</v>
+        <v>0.9945103620470628</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8180802879202024</v>
+        <v>0.8156148870671459</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9943255528123531</v>
+        <v>0.9986545955373483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9863250866823713</v>
+        <v>0.9945103620470628</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8180802879202024</v>
+        <v>0.8156148870671459</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9136285922222629</v>
+        <v>0.9164471254107359</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1824</v>
+        <v>2250</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch61_r0.01_Ld0.7_Lp0.3_seed896</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[61]</t>
+          <t>[76]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9997342132337127</v>
+        <v>0.9943255528123531</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9681439939378569</v>
+        <v>0.9863250866823713</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7821562297202032</v>
+        <v>0.8180802879202024</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9997342132337127</v>
+        <v>0.9943255528123531</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9681439939378569</v>
+        <v>0.9863250866823713</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7821562297202032</v>
+        <v>0.8180802879202024</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8957548362497907</v>
+        <v>0.9136285922222629</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1646</v>
+        <v>2843</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[55]</t>
+          <t>[94]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.999716109564902</v>
+        <v>0.9992522452713695</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9929671224177284</v>
+        <v>0.9876614333285169</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7568444068842077</v>
+        <v>0.8012379875171317</v>
       </c>
       <c r="G4" t="n">
-        <v>0.999716109564902</v>
+        <v>0.9992522452713695</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9929671224177284</v>
+        <v>0.9876614333285169</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7568444068842077</v>
+        <v>0.8012379875171317</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8935126259935222</v>
+        <v>0.9089771673284873</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1982</v>
+        <v>2666</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[67]</t>
+          <t>[88]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9987194250144719</v>
+        <v>0.9997339220831416</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9826826957237216</v>
+        <v>0.982150314957204</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6405444787210259</v>
+        <v>0.794741027950464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9987194250144719</v>
+        <v>0.9997339220831416</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9826826957237216</v>
+        <v>0.982150314957204</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6405444787210259</v>
+        <v>0.794741027950464</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8450101828354796</v>
+        <v>0.90492459530203</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1809</v>
+        <v>2876</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[61]</t>
+          <t>[95]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9993760084036005</v>
+        <v>0.9902086044674883</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9789849068812012</v>
+        <v>0.9804747537246968</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6351813041384023</v>
+        <v>0.8032319521603384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9993760084036005</v>
+        <v>0.9902086044674883</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9789849068812012</v>
+        <v>0.9804747537246968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6351813041384023</v>
+        <v>0.8032319521603384</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8420053673530729</v>
+        <v>0.9048666840882841</v>
       </c>
     </row>
   </sheetData>
